--- a/jogos_2024-10-11.xlsx
+++ b/jogos_2024-10-11.xlsx
@@ -643,16 +643,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hrvatski Dragovoljac</t>
+          <t>Zrinski Jurjevac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trnje</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -669,34 +669,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -720,14 +720,14 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45576.4375</v>
@@ -901,16 +901,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grobničan Čavle</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -927,65 +927,65 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45576.4375</v>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grobničan Čavle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1185,65 +1185,65 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45576.4375</v>
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinski Jurjevac</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="P7" t="n">
         <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45576.4375</v>
@@ -1417,20 +1417,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>NK Bjelovar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1443,49 +1443,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1494,21 +1494,21 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>['-1']</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45576.4375</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NK Bjelovar</t>
+          <t>Dugo Selo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Radnik Križevci</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dugo Selo</t>
+          <t>Hrvatski Dragovoljac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Radnik Križevci</t>
+          <t>Trnje</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>3</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1833,80 +1833,80 @@
         <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['11', '45', '68']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.75</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['7', '45+4', '86']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['38', '66']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45576.5</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1962,80 +1962,80 @@
         <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.63</v>
       </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.57</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['7', '45+4', '86']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['38', '66']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AH12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['11', '45', '68']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45576.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '38', '83']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45576.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['27', '38', '83']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45576.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2346,55 +2346,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.17</v>
       </c>
       <c r="AC15" t="n">
         <v>2.25</v>
@@ -2409,20 +2409,20 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45576.64583333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2464,10 +2464,10 @@
         <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,55 +2475,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.49</v>
+        <v>2.88</v>
       </c>
       <c r="O16" t="n">
         <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
         <v>2.2</v>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['11', '50']</t>
+          <t>['5', '42']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['74', '79', '87']</t>
+          <t>['12', '45+5', '90+7']</t>
         </is>
       </c>
       <c r="AG16" t="n">
         <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45576.64583333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.53</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45576.64583333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,55 +2733,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.44</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
         <v>2</v>
@@ -2791,25 +2791,25 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45576.64583333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,23 +2836,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4.2</v>
       </c>
-      <c r="N19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>3.95</v>
       </c>
       <c r="U19" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['11', '50']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['74', '79', '87']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45576.64583333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Turris Neapolis</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>3</v>
-      </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="AD20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['15', '54']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.88</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['5', '42']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['12', '45+5', '90+7']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45576.64583333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
         <v>1.5</v>
@@ -3144,41 +3144,41 @@
         <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['22', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45576.64583333334</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turris Neapolis</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,34 +3249,34 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
         <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
         <v>1.03</v>
@@ -3288,44 +3288,44 @@
         <v>2.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB22" t="n">
         <v>1.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['22', '60']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['15', '54']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45576.64583333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="O23" t="n">
         <v>2.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.36</v>
       </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['47', '75']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['36', '73']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.63</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45576.65625</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3496,10 +3496,10 @@
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,70 +3507,70 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['47', '75']</t>
+          <t>['4', '78']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['36', '73']</t>
+          <t>['48', '69']</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45576.65625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
         <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
@@ -3660,10 +3660,10 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
         <v>1.9</v>
@@ -3687,19 +3687,19 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['4', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['48', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45576.65625</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.6</v>
+        <v>3.81</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="N26" t="n">
-        <v>5.75</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3816,19 +3816,19 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['44', '48', '57', '90+4']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG26" t="n">
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45576.65625</v>
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.81</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>3.44</v>
+        <v>4.25</v>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>5.69</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.5</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
       <c r="U27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['62', '72', '86', '88']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.36</v>
       </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['44', '48', '57', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45576.65625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,34 +4023,34 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M28" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="N28" t="n">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
         <v>5.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -4062,31 +4062,31 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD28" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['62', '72', '86', '88']</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AJ28" t="n">
         <v>3.25</v>
